--- a/data/trans_orig/IP1004-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP1004-Clase-trans_orig.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5682</t>
+          <t>5549</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4789</t>
+          <t>4878</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>81707</t>
+          <t>81840</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>168570</t>
+          <t>168481</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3389</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3224</t>
+          <t>3515</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>95943</t>
+          <t>96248</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>163500</t>
+          <t>163209</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2703</t>
+          <t>3990</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>3359</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>199371</t>
+          <t>198084</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>399439</t>
+          <t>399448</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>593</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5408</t>
+          <t>5867</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5672</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>121881</t>
+          <t>121422</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>126698</t>
+          <t>126696</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>225738</t>
+          <t>226103</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>5561</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7290</t>
+          <t>7300</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9136</t>
+          <t>9248</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>633823</t>
+          <t>633295</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>677313</t>
+          <t>677303</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>683339</t>
+          <t>683318</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1314323</t>
+          <t>1314211</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1321535</t>
+          <t>1321503</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4019</t>
+          <t>3988</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>3647</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>5529</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>84420</t>
+          <t>84451</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>85570</t>
+          <t>86116</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>173445</t>
+          <t>172674</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3766</t>
+          <t>3719</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>223098</t>
+          <t>223145</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>428742</t>
+          <t>428959</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>4480</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>743</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6875</t>
+          <t>6163</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>670116</t>
+          <t>669601</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>708174</t>
+          <t>708468</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1380707</t>
+          <t>1381419</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1387166</t>
+          <t>1386839</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,97%</t>
+          <t>99,95%</t>
         </is>
       </c>
     </row>
@@ -7036,7 +7036,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3113</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -7144,7 +7144,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>220477</t>
+          <t>219712</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>430560</t>
+          <t>431318</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7722,7 +7722,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2993</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7792,7 +7792,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3232</t>
+          <t>2983</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>58094</t>
+          <t>58097</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>125680</t>
+          <t>125929</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -7915,7 +7915,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8065,7 +8065,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>4780</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8135,7 +8135,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>4653</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -8173,7 +8173,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>666726</t>
+          <t>666722</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1376234</t>
+          <t>1376586</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">

--- a/data/trans_orig/IP1004-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP1004-Clase-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -835,47 +835,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>104352</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>104352</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>104352</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>104352</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,107 +1065,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1415</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5549</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4914</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,62%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,35%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>5,62%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1415</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4353</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1415</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4878</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>85974</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>81840</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>82475</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>87389</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,38%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>93,65%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>94,38%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>258</t>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>168481</t>
+          <t>169006</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1296,52 +1296,52 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
           <t>87389</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>87389</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>87389</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,107 +1408,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>618</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>618</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3084</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3130</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,1%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>618</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3515</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>98714</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>96208</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,38%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,85%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>67392</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>98714</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>96248</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,38%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>163209</t>
+          <t>163594</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,84 +1751,84 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>667</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>667</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3990</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3359</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1869,67 +1869,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>201407</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>198203</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,67%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,08%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>200733</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>201407</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>198084</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,67%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>399448</t>
+          <t>399456</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>303</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>200733</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>200733</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>200733</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,92 +2094,92 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>590</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,09%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1970</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>593</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5867</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>4,61%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>593</t>
-        </is>
-      </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>5364</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>125319</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>122089</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>126699</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,45%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,91%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,54%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>104120</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>125319</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>121422</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>126696</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,45%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>226103</t>
+          <t>226046</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>104120</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>104120</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>104120</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2550,47 +2550,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>74870</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2780,72 +2780,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>3255</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1138</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>7176</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>1415</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>5561</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>4326</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,22%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>3255</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>1285</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>7300</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9248</t>
+          <t>9523</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -2893,74 +2893,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>681348</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>677427</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>683465</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,52%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>98,95%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,83%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>951</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>637441</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>633295</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>634530</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>638856</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,78%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>99,13%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>99,32%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1024</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>681348</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>677303</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>683318</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,52%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>98,93%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,81%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>1975</t>
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1314211</t>
+          <t>1313936</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1321503</t>
+          <t>1321440</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1029</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>953</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>638856</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>638856</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>638856</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1029</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3189,7 +3189,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3362,102 +3362,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3939</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,39%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>790</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3988</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4119</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,89%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,51%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>777</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3647</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>4,66%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1568</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5440</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1568</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5529</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -3470,74 +3470,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>88986</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>85824</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,13%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>95,61%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>87649</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>84451</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>84320</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>88439</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,11%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,49%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,34%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>88986</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>86116</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,13%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>95,94%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>256</t>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>172674</t>
+          <t>172763</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3583,57 +3583,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>88439</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>88439</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>88439</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3813,47 +3813,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>92729</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -3926,57 +3926,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>92729</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>92729</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>92729</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4156,47 +4156,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>84205</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -4269,57 +4269,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>84205</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>84205</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>84205</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4386,107 +4386,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>744</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3739</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>744</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3719</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>5092</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>744</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3533</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -4499,72 +4499,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>226120</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>223125</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,67%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,35%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>298</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>205628</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>226120</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>223145</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,67%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>428959</t>
+          <t>427400</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4612,57 +4612,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>298</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>205628</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>205628</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>205628</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4842,47 +4842,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>149169</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -4955,57 +4955,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5185,47 +5185,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>53911</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -5298,57 +5298,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1522</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>5259</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>790</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>4480</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3975</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,12%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>1522</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>5033</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>742</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6163</t>
+          <t>6854</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -5528,74 +5528,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1016</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>711979</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>708242</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,79%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>99,26%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>972</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>673291</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>669601</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>670106</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>674081</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,88%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>99,34%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>99,41%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1016</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>711979</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>708468</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,79%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>99,29%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>1988</t>
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1381419</t>
+          <t>1380728</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1386839</t>
+          <t>1386840</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -5641,57 +5641,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1018</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>973</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>674081</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>674081</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>674081</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1018</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5813,7 +5813,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5824,7 +5824,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6105,47 +6105,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>83090</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -6218,57 +6218,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6448,47 +6448,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>105714</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -6561,57 +6561,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>105714</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>105714</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>105714</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6791,47 +6791,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>61840</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -6904,57 +6904,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7021,72 +7021,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>771</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3865</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4254</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3113</t>
+          <t>3122</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7134,74 +7134,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>222806</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>219712</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>219323</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,66%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,27%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,1%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>641</t>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>431318</t>
+          <t>431309</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -7247,57 +7247,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7477,47 +7477,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>136194</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -7590,57 +7590,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7707,107 +7707,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>589</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>2990</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2935</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,96%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>589</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>2969</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>589</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>2983</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -7820,74 +7820,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>60498</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>58097</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>58152</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>99,04%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>95,1%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>95,2%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>185</t>
@@ -7900,7 +7900,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>125929</t>
+          <t>125943</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -7915,7 +7915,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -7933,57 +7933,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8050,107 +8050,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>1360</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>4780</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>4987</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>5305</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1360</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>4653</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -8163,74 +8163,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1011</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>670142</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>666722</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>666515</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>671502</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,8%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>99,29%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>99,26%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1017</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>2028</t>
@@ -8243,7 +8243,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1376586</t>
+          <t>1375934</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8276,57 +8276,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>1013</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>671502</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>671502</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>671502</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1017</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
